--- a/artfynd/A 57803-2021 artfynd.xlsx
+++ b/artfynd/A 57803-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 57803-2021 artfynd.xlsx
+++ b/artfynd/A 57803-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -925,6 +925,134 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>106083466</v>
+      </c>
+      <c r="B4" t="n">
+        <v>56453</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Godkänd baserat på observatörens uppgifter</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Nordost slängbäcken, Nrk</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>531888</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6584207</v>
+      </c>
+      <c r="S4" t="n">
+        <v>50</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Fellingsbro</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2023-01-21</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>10:09</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2023-01-21</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>10:09</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Johan Wretenberg</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Johan Wretenberg</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 57803-2021 artfynd.xlsx
+++ b/artfynd/A 57803-2021 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>59070965</v>
       </c>
       <c r="B2" t="n">
-        <v>90676</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -725,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>531888.0374189583</v>
+        <v>531888</v>
       </c>
       <c r="R2" t="n">
-        <v>6584207.086722708</v>
+        <v>6584207</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -758,19 +753,9 @@
           <t>2015-10-17</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2015-10-17</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -803,37 +788,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>106083467</v>
+        <v>106083466</v>
       </c>
       <c r="B3" t="n">
-        <v>56540</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -842,10 +822,14 @@
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -855,10 +839,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>531888.0374189583</v>
+        <v>531888</v>
       </c>
       <c r="R3" t="n">
-        <v>6584207.086722708</v>
+        <v>6584207</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -927,37 +911,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>106083466</v>
+        <v>106083467</v>
       </c>
       <c r="B4" t="n">
-        <v>56478</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -966,14 +945,10 @@
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>

--- a/artfynd/A 57803-2021 artfynd.xlsx
+++ b/artfynd/A 57803-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -785,6 +790,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/59070965</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -908,6 +918,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106083466</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1027,8 +1042,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106083467</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>